--- a/jogos_2026-02-15.xlsx
+++ b/jogos_2026-02-15.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>2.61</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.72</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>7.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.83</v>
+        <v>3.24</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N33" t="n">
-        <v>4.02</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>3.22</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.29</v>
+        <v>2.53</v>
       </c>
       <c r="M37" t="n">
-        <v>5.9</v>
+        <v>3.42</v>
       </c>
       <c r="N37" t="n">
-        <v>10.5</v>
+        <v>2.55</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.53</v>
+        <v>1.29</v>
       </c>
       <c r="M38" t="n">
-        <v>3.42</v>
+        <v>5.9</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>10.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>9.34</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>9.34</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>7.61</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>12.31</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7.61</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>12.31</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="M59" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="N59" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,17 +7676,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.68</v>
+        <v>1.09</v>
       </c>
       <c r="M66" t="n">
-        <v>3.36</v>
+        <v>8</v>
       </c>
       <c r="N66" t="n">
-        <v>2.49</v>
+        <v>29</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="M67" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="N67" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.09</v>
+        <v>2.66</v>
       </c>
       <c r="M68" t="n">
-        <v>8</v>
+        <v>3.48</v>
       </c>
       <c r="N68" t="n">
-        <v>29</v>
+        <v>2.45</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="M82" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>2.99</v>
+        <v>2.15</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Voghera</t>
+          <t>Sambiase</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Varesina</t>
+          <t>Igea Virtus</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Città di Fasano</t>
+          <t>Paternò</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Francavilla</t>
+          <t>Sancataldese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Afragolese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nardò</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paganese</t>
+          <t>Mestre</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pompei</t>
+          <t>Vigasio</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gravina</t>
+          <t>Altavilla</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>Campodarsego</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Puteolana</t>
+          <t>Legnago Salus</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fidelis Andria</t>
+          <t>Clodiense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ferrandina</t>
+          <t>L'Aquila</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>ACD Maceratese</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Termoli Calcio</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Real Giulianova Ssd</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Martina Franca</t>
+          <t>CastrumFavara</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Manfredonia</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CynthiAlbalonga</t>
+          <t>Teramo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Monterotondo Scalo</t>
+          <t>Fossombrone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Città di Fasano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sondrio</t>
+          <t>Virtus Francavilla</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Castellanzese</t>
+          <t>Afragolese</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Villa Valle</t>
+          <t>Nardò</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Virtus Ciserano Bergamo</t>
+          <t>Paganese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Oltrepò</t>
+          <t>Pompei</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Gravina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brusaporto</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Casatese</t>
+          <t>Ancona 1905</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Calepina</t>
+          <t>Chieti</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Scanzorosciate</t>
+          <t>Ferrandina</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Heraclea</t>
+          <t>Martina Franca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Acerrana</t>
+          <t>Manfredonia</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>4.84</v>
+        <v>3.29</v>
       </c>
       <c r="M103" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="N103" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aversa Normanna</t>
+          <t>Imperia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sarnese</t>
+          <t>Valenzana</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Città di Varese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Breno</t>
+          <t>Ligorna</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Anzio</t>
+          <t>Heraclea</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sarrabus Ogliastra</t>
+          <t>Real Acerrana</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olbia</t>
+          <t>Aversa Normanna</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Montespaccato</t>
+          <t>Sarnese</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CastrumFavara</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Puteolana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Fidelis Andria</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AC Palermo</t>
+          <t>Recanatese</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Reggina</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Messina</t>
+          <t>AC Palermo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Nissa</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vigor Lamezia</t>
+          <t>Calvi Noale</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Ischia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Recanatese</t>
+          <t>Flaminia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Atletico Ascoli</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Castelfidardo Calcio</t>
+          <t>Brusaporto</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Obermais</t>
+          <t>Nocerina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bassano Virtus</t>
+          <t>Budoni</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Calvi Noale</t>
+          <t>Atletico Lodigiani</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Luparense</t>
+          <t>Conegliano</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brian Lignano</t>
+          <t>Portosummaga</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gelbison</t>
+          <t>Casatese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ragusa</t>
+          <t>Real Calepina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Marino Calcio</t>
+          <t>Virtus Ciserano Bergamo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Unipomezia</t>
+          <t>Oltrepò</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Milazzo</t>
+          <t>Este</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vibonese</t>
+          <t>Cjarlins Muzane</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Nicolò</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vigor Senigallia</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trastevere</t>
+          <t>Castellanzese</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Valmontone</t>
+          <t>Villa Valle</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sammaurese</t>
+          <t>CynthiAlbalonga</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sora</t>
+          <t>Real Monterotondo Scalo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>USD Palmese</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cassino</t>
+          <t>Sondrio</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Teramo</t>
+          <t>Olbia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fossombrone</t>
+          <t>Montespaccato</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ischia</t>
+          <t>San Luigi</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Flaminia</t>
+          <t>Adriese</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.84</v>
+        <v>4.84</v>
       </c>
       <c r="M128" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>1.72</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cittadella Vis Modena</t>
+          <t>Luparense</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pro Sesto</t>
+          <t>Brian Lignano</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Termoli Calcio</t>
+          <t>Reggina</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Giulianova Ssd</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>L'Aquila</t>
+          <t>Nissa</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ACD Maceratese</t>
+          <t>Vigor Lamezia</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Luigi</t>
+          <t>Atletico Ascoli</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Adriese</t>
+          <t>Castelfidardo Calcio</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Legnago Salus</t>
+          <t>Scanzorosciate</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Clodiense</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nocerina</t>
+          <t>USD Palmese</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Budoni</t>
+          <t>Cassino</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Altavilla</t>
+          <t>Gelbison</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Campodarsego</t>
+          <t>Ragusa</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Obermais</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Bassano Virtus</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Paternò</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sancataldese</t>
+          <t>Breno</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sambiase</t>
+          <t>Chievo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Igea Virtus</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mestre</t>
+          <t>San Nicolò</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vigasio</t>
+          <t>Vigor Senigallia</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Trastevere</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Atletico Lodigiani</t>
+          <t>Valmontone</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ancona 1905</t>
+          <t>Voghera</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Chieti</t>
+          <t>Varesina</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Conegliano</t>
+          <t>Sammaurese</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Portosummaga</t>
+          <t>Sora</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Este</t>
+          <t>San Marino Calcio</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cjarlins Muzane</t>
+          <t>Unipomezia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chievo</t>
+          <t>Milazzo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Vibonese</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Poggibonsi</t>
+          <t>Cittadella Vis Modena</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Foligno</t>
+          <t>Pro Sesto</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Anzio</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Sarrabus Ogliastra</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Terranuova Traiana</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Ghivizzano Borgo Mozzano</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sansepolcro</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Prato</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Derthona</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Chisola</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Saluzzo</t>
+          <t>Poggibonsi</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lavagnese</t>
+          <t>Foligno</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Orvietana Calcio</t>
+          <t>Scandicci</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Montevarchi Calcio</t>
+          <t>Seravezza</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pro Palazzolo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Correggese</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Asti</t>
+          <t>Orvietana Calcio</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NovaRomentin</t>
+          <t>Montevarchi Calcio</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Trevigliese</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sasso Marconi</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cannara</t>
+          <t>Tau Altopascio</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FC Siena</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Scandicci</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Seravezza</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Imperia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Valenzana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tau Altopascio</t>
+          <t>Coriano</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Crema</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Sasso Marconi</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Gavorrano</t>
+          <t>Camaiore Calcio</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>San Donato Tavarnelle</t>
+          <t>Sporting Trestina</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Camaiore Calcio</t>
+          <t>Rovato Vertova</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sporting Trestina</t>
+          <t>Sant'Angelo</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Gavorrano</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Trevigliese</t>
+          <t>San Donato Tavarnelle</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Terranuova Traiana</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ghivizzano Borgo Mozzano</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rovato Vertova</t>
+          <t>Asti</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sant'Angelo</t>
+          <t>NovaRomentin</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sansepolcro</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Prato</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Pro Palazzolo</t>
+          <t>Cannara</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Correggese</t>
+          <t>FC Siena</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Coriano</t>
+          <t>Celle Varazze</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Crema</t>
+          <t>Cairese</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Celle Varazze</t>
+          <t>Pistoiese</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Cairese</t>
+          <t>Tuttocuoio</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Pistoiese</t>
+          <t>Saluzzo</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tuttocuoio</t>
+          <t>Lavagnese</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Città di Varese</t>
+          <t>Derthona</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ligorna</t>
+          <t>Chisola</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="M176" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N176" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.42</v>
+        <v>4.03</v>
       </c>
       <c r="M178" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N178" t="n">
-        <v>2.92</v>
+        <v>1.71</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Latte Dolce</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Latte Dolce</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8.9</v>
+        <v>2.41</v>
       </c>
       <c r="M182" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N182" t="n">
-        <v>1.31</v>
+        <v>2.7</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>3.96</v>
+        <v>8.9</v>
       </c>
       <c r="M183" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="N183" t="n">
-        <v>2.17</v>
+        <v>1.31</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.37</v>
+        <v>3.04</v>
       </c>
       <c r="M184" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N184" t="n">
-        <v>3.62</v>
+        <v>2.65</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="M187" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N187" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.25</v>
+        <v>1.74</v>
       </c>
       <c r="M196" t="n">
-        <v>3.27</v>
+        <v>3.96</v>
       </c>
       <c r="N196" t="n">
-        <v>2.18</v>
+        <v>5.33</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="M197" t="n">
-        <v>3.96</v>
+        <v>3.72</v>
       </c>
       <c r="N197" t="n">
-        <v>5.33</v>
+        <v>4.61</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24385,10 +24385,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>4.11</v>
+        <v>1.32</v>
       </c>
       <c r="M202" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="N202" t="n">
-        <v>1.92</v>
+        <v>9.9</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24504,10 +24504,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.27</v>
+        <v>5.36</v>
       </c>
       <c r="M210" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="N210" t="n">
-        <v>3.43</v>
+        <v>1.47</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="M230" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N230" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB230" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB233" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC233" t="n">
         <v>0</v>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="M243" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N243" t="n">
-        <v>1.71</v>
+        <v>3.25</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29383,10 +29383,10 @@
         <v>0</v>
       </c>
       <c r="AA243" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB243" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC243" t="n">
         <v>0</v>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29457,55 +29457,55 @@
         </is>
       </c>
       <c r="L244" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M244" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N244" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="n">
+        <v>0</v>
+      </c>
+      <c r="V244" t="n">
+        <v>0</v>
+      </c>
+      <c r="W244" t="n">
+        <v>0</v>
+      </c>
+      <c r="X244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA244" t="n">
         <v>2</v>
       </c>
-      <c r="M244" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N244" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
-      <c r="S244" t="n">
-        <v>0</v>
-      </c>
-      <c r="T244" t="n">
-        <v>0</v>
-      </c>
-      <c r="U244" t="n">
-        <v>0</v>
-      </c>
-      <c r="V244" t="n">
-        <v>0</v>
-      </c>
-      <c r="W244" t="n">
-        <v>0</v>
-      </c>
-      <c r="X244" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y244" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z244" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA244" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB244" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC244" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29740,10 +29740,10 @@
         <v>0</v>
       </c>
       <c r="AA246" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC246" t="n">
         <v>0</v>
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="M247" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N247" t="n">
-        <v>2.76</v>
+        <v>3.46</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB248" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC248" t="n">
         <v>0</v>
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="M249" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N249" t="n">
-        <v>3.46</v>
+        <v>2.76</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>2.63</v>
+        <v>11</v>
       </c>
       <c r="M250" t="n">
-        <v>3.14</v>
+        <v>5.5</v>
       </c>
       <c r="N250" t="n">
-        <v>2.68</v>
+        <v>1.27</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30216,10 +30216,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AB250" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC250" t="n">
         <v>0</v>
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="M257" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N257" t="n">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB257" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="M259" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N259" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31287,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AA259" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32313,13 +32313,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32551,13 +32551,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="M273" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="N273" t="n">
-        <v>3.88</v>
+        <v>2.97</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32953,10 +32953,10 @@
         <v>0</v>
       </c>
       <c r="AA273" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB273" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC273" t="n">
         <v>0</v>
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="M274" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="N274" t="n">
-        <v>2.97</v>
+        <v>3.88</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33072,10 +33072,10 @@
         <v>0</v>
       </c>
       <c r="AA274" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AB274" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC274" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33316,10 +33316,10 @@
         <v>0</v>
       </c>
       <c r="AC276" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD276" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE276" t="n">
         <v>0</v>
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="M279" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N279" t="n">
-        <v>3.23</v>
+        <v>5.17</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M280" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N280" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34268,10 +34268,10 @@
         <v>0</v>
       </c>
       <c r="AC284" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD284" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.59</v>
+        <v>2.46</v>
       </c>
       <c r="M285" t="n">
-        <v>3.84</v>
+        <v>2.86</v>
       </c>
       <c r="N285" t="n">
-        <v>4.55</v>
+        <v>2.82</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB289" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -34931,13 +34931,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -34976,10 +34976,10 @@
         <v>0</v>
       </c>
       <c r="AA290" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC290" t="n">
         <v>0</v>
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35050,13 +35050,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M291" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35169,13 +35169,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="M292" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N292" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -35214,10 +35214,10 @@
         <v>0</v>
       </c>
       <c r="AA292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB292" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC292" t="n">
         <v>0</v>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35288,13 +35288,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M293" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35407,13 +35407,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -35452,10 +35452,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB294" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC294" t="n">
         <v>0</v>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.92</v>
+        <v>1.93</v>
       </c>
       <c r="M295" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="N295" t="n">
-        <v>2.29</v>
+        <v>3.82</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35609,7 +35609,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35883,13 +35883,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="M298" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="N298" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="AA298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB298" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC298" t="n">
         <v>0</v>
@@ -35966,7 +35966,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -35976,12 +35976,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36002,13 +36002,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N299" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -36047,10 +36047,10 @@
         <v>0</v>
       </c>
       <c r="AA299" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB299" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36121,13 +36121,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>2.17</v>
+        <v>1.69</v>
       </c>
       <c r="M300" t="n">
-        <v>3.28</v>
+        <v>3.91</v>
       </c>
       <c r="N300" t="n">
-        <v>3.33</v>
+        <v>5.01</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -36166,10 +36166,10 @@
         <v>0</v>
       </c>
       <c r="AA300" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB300" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC300" t="n">
         <v>0</v>
@@ -36204,7 +36204,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -36214,12 +36214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -36240,13 +36240,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -36442,7 +36442,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -36452,12 +36452,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -36478,13 +36478,13 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N303" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O303" t="n">
         <v>0</v>
@@ -36523,10 +36523,10 @@
         <v>0</v>
       </c>
       <c r="AA303" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB303" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC303" t="n">
         <v>0</v>
@@ -36561,7 +36561,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -36571,12 +36571,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -36597,13 +36597,13 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="M304" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N304" t="n">
-        <v>3.91</v>
+        <v>1.85</v>
       </c>
       <c r="O304" t="n">
         <v>0</v>
@@ -36642,10 +36642,10 @@
         <v>0</v>
       </c>
       <c r="AA304" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB304" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC304" t="n">
         <v>0</v>
@@ -36918,7 +36918,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -36928,12 +36928,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -36954,13 +36954,13 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M307" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O307" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -37047,12 +37047,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -37073,13 +37073,13 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N308" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O308" t="n">
         <v>0</v>
@@ -37751,22 +37751,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -37787,13 +37787,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M314" t="n">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="N314" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -37832,10 +37832,10 @@
         <v>0</v>
       </c>
       <c r="AA314" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB314" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC314" t="n">
         <v>0</v>
@@ -37870,22 +37870,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -37906,13 +37906,13 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="M315" t="n">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="N315" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="O315" t="n">
         <v>0</v>
@@ -37951,10 +37951,10 @@
         <v>0</v>
       </c>
       <c r="AA315" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB315" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC315" t="n">
         <v>0</v>
@@ -37989,7 +37989,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -37999,12 +37999,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -38108,7 +38108,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -38118,12 +38118,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -38227,22 +38227,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -38263,13 +38263,13 @@
         </is>
       </c>
       <c r="L318" t="n">
-        <v>2.11</v>
+        <v>1.29</v>
       </c>
       <c r="M318" t="n">
-        <v>2.73</v>
+        <v>5</v>
       </c>
       <c r="N318" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="O318" t="n">
         <v>0</v>
@@ -38346,22 +38346,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -38382,13 +38382,13 @@
         </is>
       </c>
       <c r="L319" t="n">
-        <v>1.29</v>
+        <v>2.11</v>
       </c>
       <c r="M319" t="n">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="N319" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="O319" t="n">
         <v>0</v>

--- a/jogos_2026-02-15.xlsx
+++ b/jogos_2026-02-15.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>3.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>2.72</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>7.5</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>3.28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.28</v>
+        <v>2.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>7.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>2.74</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>2.51</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>3.24</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N23" t="n">
-        <v>3.22</v>
+        <v>2.11</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.89</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.74</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.51</v>
+        <v>4.02</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="M30" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="N30" t="n">
-        <v>7.5</v>
+        <v>4.69</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.24</v>
+        <v>1.29</v>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.7</v>
+        <v>3.89</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>4.02</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.53</v>
+        <v>1.29</v>
       </c>
       <c r="M37" t="n">
-        <v>3.42</v>
+        <v>5.9</v>
       </c>
       <c r="N37" t="n">
-        <v>2.55</v>
+        <v>10.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>9.34</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="M52" t="n">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="N52" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="M53" t="n">
-        <v>7.61</v>
+        <v>3.04</v>
       </c>
       <c r="N53" t="n">
-        <v>12.31</v>
+        <v>4.44</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="M56" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="N56" t="n">
-        <v>4.44</v>
+        <v>2.95</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="M59" t="n">
-        <v>3.22</v>
+        <v>5.42</v>
       </c>
       <c r="N59" t="n">
-        <v>2.9</v>
+        <v>9.34</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,17 +7676,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>7.61</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>12.31</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>5</v>
+        <v>2.11</v>
       </c>
       <c r="M79" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>1.57</v>
+        <v>3.21</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="M81" t="n">
         <v>3.6</v>
       </c>
       <c r="N81" t="n">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="M83" t="n">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sambiase</t>
+          <t>Paternò</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Igea Virtus</t>
+          <t>Sancataldese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Paternò</t>
+          <t>Mestre</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sancataldese</t>
+          <t>Vigasio</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ancona 1905</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Chieti</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mestre</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vigasio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Termoli Calcio</t>
+          <t>Sambiase</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Giulianova Ssd</t>
+          <t>Igea Virtus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CastrumFavara</t>
+          <t>Termoli Calcio</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Real Giulianova Ssd</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Teramo</t>
+          <t>Puteolana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fossombrone</t>
+          <t>Fidelis Andria</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Città di Fasano</t>
+          <t>Teramo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Virtus Francavilla</t>
+          <t>Fossombrone</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Afragolese</t>
+          <t>Città di Fasano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nardò</t>
+          <t>Virtus Francavilla</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Paganese</t>
+          <t>Afragolese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pompei</t>
+          <t>Nardò</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gravina</t>
+          <t>Paganese</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Francavilla</t>
+          <t>Pompei</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group H</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ancona 1905</t>
+          <t>Gravina</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chieti</t>
+          <t>Francavilla</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie D Group H</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Puteolana</t>
+          <t>Gela</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fidelis Andria</t>
+          <t>Acireale</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>CastrumFavara</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Recanatese</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Reggina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AC Palermo</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Casatese</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Real Calepina</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Virtus Ciserano Bergamo</t>
+          <t>San Luigi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Oltrepò</t>
+          <t>Adriese</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie D Group C</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Este</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cjarlins Muzane</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Virtus Ciserano Bergamo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Oltrepò</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CynthiAlbalonga</t>
+          <t>Olbia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Monterotondo Scalo</t>
+          <t>Montespaccato</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Olbia</t>
+          <t>Anzio</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Montespaccato</t>
+          <t>Sarrabus Ogliastra</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Luigi</t>
+          <t>Este</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Adriese</t>
+          <t>Cjarlins Muzane</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gela</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Acireale</t>
+          <t>AC Palermo</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Casatese</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Real Calepina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Reggina</t>
+          <t>Nissa</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Messina</t>
+          <t>Vigor Lamezia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nissa</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vigor Lamezia</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie D Group F</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atletico Ascoli</t>
+          <t>USD Palmese</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Castelfidardo Calcio</t>
+          <t>Cassino</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Scanzorosciate</t>
+          <t>Atletico Ascoli</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Castelfidardo Calcio</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>USD Palmese</t>
+          <t>Scanzorosciate</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cassino</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie D Group I</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gelbison</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ragusa</t>
+          <t>Breno</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group I</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Gelbison</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Breno</t>
+          <t>Ragusa</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie D Group B</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chievo</t>
+          <t>Trastevere</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Valmontone</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie D Group B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Trastevere</t>
+          <t>Chievo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Valmontone</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group F</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cittadella Vis Modena</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pro Sesto</t>
+          <t>Recanatese</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Anzio</t>
+          <t>CynthiAlbalonga</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sarrabus Ogliastra</t>
+          <t>Real Monterotondo Scalo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Terranuova Traiana</t>
+          <t>Club Milano</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ghivizzano Borgo Mozzano</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sansepolcro</t>
+          <t>Pro Palazzolo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Prato</t>
+          <t>Correggese</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Rovato Vertova</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sant'Angelo</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Poggibonsi</t>
+          <t>Scandicci</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Foligno</t>
+          <t>Seravezza</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Scandicci</t>
+          <t>Cittadella Vis Modena</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Seravezza</t>
+          <t>Pro Sesto</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Pro Palazzolo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Correggese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Orvietana Calcio</t>
+          <t>Sasso Marconi</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Montevarchi Calcio</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Trevigliese</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Cannara</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>FC Siena</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pistoiese</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Tuttocuoio</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tau Altopascio</t>
+          <t>Orvietana Calcio</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Montevarchi Calcio</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sansepolcro</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Prato</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Tau Altopascio</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sasso Marconi</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Camaiore Calcio</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sporting Trestina</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rovato Vertova</t>
+          <t>Asti</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sant'Angelo</t>
+          <t>NovaRomentin</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy Serie D Group E</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gavorrano</t>
+          <t>Saluzzo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>San Donato Tavarnelle</t>
+          <t>Lavagnese</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Derthona</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Chisola</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Asti</t>
+          <t>Poggibonsi</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NovaRomentin</t>
+          <t>Foligno</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cannara</t>
+          <t>Terranuova Traiana</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FC Siena</t>
+          <t>Ghivizzano Borgo Mozzano</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie D Group D</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Celle Varazze</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Cairese</t>
+          <t>Trevigliese</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie D Group D</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pistoiese</t>
+          <t>Camaiore Calcio</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tuttocuoio</t>
+          <t>Sporting Trestina</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie D Group E</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saluzzo</t>
+          <t>Gavorrano</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lavagnese</t>
+          <t>San Donato Tavarnelle</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Derthona</t>
+          <t>Celle Varazze</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Chisola</t>
+          <t>Cairese</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Club Milano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="M176" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N176" t="n">
-        <v>2.92</v>
+        <v>4.69</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie D Group G</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Latte Dolce</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>4.03</v>
+        <v>2.42</v>
       </c>
       <c r="M178" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N178" t="n">
-        <v>1.71</v>
+        <v>2.92</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie D Group G</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Latte Dolce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie D Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Sanremo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>AS Biellese 1902</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>3.04</v>
+        <v>2.37</v>
       </c>
       <c r="M184" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N184" t="n">
-        <v>2.65</v>
+        <v>3.62</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="M185" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N185" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie D Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sanremo</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AS Biellese 1902</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M187" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N187" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="M190" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N190" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23671,10 +23671,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB195" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="M197" t="n">
-        <v>3.72</v>
+        <v>3.96</v>
       </c>
       <c r="N197" t="n">
-        <v>4.61</v>
+        <v>5.33</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24504,10 +24504,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M207" t="n">
         <v>3.4</v>
       </c>
       <c r="N207" t="n">
-        <v>4.59</v>
+        <v>3.6</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>2.07</v>
+        <v>4.29</v>
       </c>
       <c r="M230" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="N230" t="n">
-        <v>3.52</v>
+        <v>1.68</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB231" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28788,10 +28788,10 @@
         <v>0</v>
       </c>
       <c r="AA238" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="M246" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="N246" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29740,10 +29740,10 @@
         <v>0</v>
       </c>
       <c r="AA246" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC246" t="n">
         <v>0</v>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB248" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="M249" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="N249" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30097,10 +30097,10 @@
         <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC249" t="n">
         <v>0</v>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="M250" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="N250" t="n">
-        <v>1.27</v>
+        <v>3.46</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30216,10 +30216,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB250" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC250" t="n">
         <v>0</v>
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2.48</v>
+        <v>1.33</v>
       </c>
       <c r="M257" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N257" t="n">
-        <v>2.73</v>
+        <v>8.65</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31049,10 +31049,10 @@
         <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB257" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.33</v>
+        <v>2.35</v>
       </c>
       <c r="M261" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N261" t="n">
-        <v>8.65</v>
+        <v>2.75</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.26</v>
+        <v>1.28</v>
       </c>
       <c r="M262" t="n">
-        <v>2.86</v>
+        <v>4.75</v>
       </c>
       <c r="N262" t="n">
-        <v>3.25</v>
+        <v>9.25</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31920,7 +31920,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>3.19</v>
+        <v>2.25</v>
       </c>
       <c r="M265" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="N265" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>2.72</v>
+        <v>1.81</v>
       </c>
       <c r="M266" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="N266" t="n">
-        <v>2.43</v>
+        <v>4.04</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="M267" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N267" t="n">
-        <v>2.8</v>
+        <v>3.37</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32313,13 +32313,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>1.81</v>
+        <v>2.53</v>
       </c>
       <c r="M268" t="n">
-        <v>3.34</v>
+        <v>2.93</v>
       </c>
       <c r="N268" t="n">
-        <v>4.04</v>
+        <v>2.67</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32432,13 +32432,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32551,13 +32551,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>1.28</v>
+        <v>3.19</v>
       </c>
       <c r="M270" t="n">
-        <v>4.75</v>
+        <v>2.99</v>
       </c>
       <c r="N270" t="n">
-        <v>9.25</v>
+        <v>2.22</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="M271" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N271" t="n">
-        <v>3.37</v>
+        <v>2.43</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="M272" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="N272" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32834,10 +32834,10 @@
         <v>0</v>
       </c>
       <c r="AA272" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB272" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC272" t="n">
         <v>0</v>
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="M273" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N273" t="n">
-        <v>2.97</v>
+        <v>3.76</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32953,10 +32953,10 @@
         <v>0</v>
       </c>
       <c r="AA273" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB273" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC273" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="M275" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N275" t="n">
-        <v>3.76</v>
+        <v>2.97</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB275" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33384,13 +33384,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="M278" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="N278" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33622,13 +33622,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="M279" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N279" t="n">
-        <v>5.17</v>
+        <v>3.8</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="M289" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB289" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -34931,13 +34931,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35169,13 +35169,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N292" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -35214,10 +35214,10 @@
         <v>0</v>
       </c>
       <c r="AA292" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB292" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC292" t="n">
         <v>0</v>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35288,13 +35288,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="M293" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N293" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -35333,10 +35333,10 @@
         <v>0</v>
       </c>
       <c r="AA293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC293" t="n">
         <v>0</v>
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35407,13 +35407,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>4.72</v>
+        <v>1.73</v>
       </c>
       <c r="M294" t="n">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="N294" t="n">
-        <v>1.68</v>
+        <v>4.33</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -35452,10 +35452,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC294" t="n">
         <v>0</v>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35526,13 +35526,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -35609,7 +35609,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N296" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -35847,7 +35847,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35883,13 +35883,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="M298" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="N298" t="n">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="AA298" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB298" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC298" t="n">
         <v>0</v>
@@ -35966,7 +35966,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -35976,12 +35976,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36002,13 +36002,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M299" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -36047,10 +36047,10 @@
         <v>0</v>
       </c>
       <c r="AA299" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB299" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36121,13 +36121,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N300" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -36166,10 +36166,10 @@
         <v>0</v>
       </c>
       <c r="AA300" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB300" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC300" t="n">
         <v>0</v>
@@ -36204,7 +36204,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -36214,12 +36214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -36240,13 +36240,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="M301" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="N301" t="n">
-        <v>3.91</v>
+        <v>2.9</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -36359,13 +36359,13 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="M302" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="N302" t="n">
-        <v>2.9</v>
+        <v>3.91</v>
       </c>
       <c r="O302" t="n">
         <v>0</v>
@@ -37751,22 +37751,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -37787,13 +37787,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="M314" t="n">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="N314" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -37832,10 +37832,10 @@
         <v>0</v>
       </c>
       <c r="AA314" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB314" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC314" t="n">
         <v>0</v>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -37880,12 +37880,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -37906,13 +37906,13 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O315" t="n">
         <v>0</v>
@@ -37951,10 +37951,10 @@
         <v>0</v>
       </c>
       <c r="AA315" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB315" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC315" t="n">
         <v>0</v>
@@ -37989,22 +37989,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -38025,13 +38025,13 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M316" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N316" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O316" t="n">
         <v>0</v>
